--- a/output/pdf_financials_xlsx/MMA.xlsx
+++ b/output/pdf_financials_xlsx/MMA.xlsx
@@ -5241,22 +5241,22 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.186667</v>
+        <v>-0.178635</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.085199</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.52124</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>3.92</v>
+        <v>1.595805</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-2.923622</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.338674</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -16070,7 +16070,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E147" s="5" t="n">
         <v>-0.365302</v>
       </c>

--- a/output/pdf_financials_xlsx/MMA.xlsx
+++ b/output/pdf_financials_xlsx/MMA.xlsx
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000401</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -867,19 +867,19 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002094</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.066108</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.002482</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.203071</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.310959</v>
       </c>
     </row>
     <row r="13">
@@ -1514,7 +1514,7 @@
         <v>-0.407009</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.891305</v>
+        <v>-0.891706</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.458917</v>
@@ -1523,19 +1523,19 @@
         <v>-0.356998</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.041855</v>
+        <v>-2.043949</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.17988</v>
+        <v>-3.245988</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.537206</v>
+        <v>-1.539688</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.348941</v>
+        <v>-3.552012</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-14.230444</v>
+        <v>-14.541403</v>
       </c>
     </row>
     <row r="28">
@@ -1594,7 +1594,7 @@
         <v>-0.407009</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.891305</v>
+        <v>-0.891706</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.458917</v>
@@ -1603,19 +1603,19 @@
         <v>-0.333598</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.018098</v>
+        <v>-2.020192</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.154248</v>
+        <v>-3.220356</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.499817</v>
+        <v>-1.502299</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.270616</v>
+        <v>-3.473687</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-14.132221</v>
+        <v>-14.44318</v>
       </c>
     </row>
     <row r="30">
@@ -1802,31 +1802,31 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.698149</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.52881</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.207875</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.006969</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.061964</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.564905</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.023883</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.310552</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>30.992806</v>
       </c>
     </row>
     <row r="35">
@@ -1882,31 +1882,31 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.698149</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.52881</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.207875</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.006969</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.061964</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.564905</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.023883</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>2.504555</v>
+        <v>7.815107</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>30.992806</v>
       </c>
     </row>
     <row r="37">
@@ -2362,31 +2362,31 @@
         <v>0.049338</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.782463</v>
+        <v>0.084314</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.586967</v>
+        <v>0.058157</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.284233</v>
+        <v>0.076358</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.028567</v>
+        <v>0.021598</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.087981</v>
+        <v>0.026017</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.630017</v>
+        <v>0.065112</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.073459</v>
+        <v>0.049576</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.525522</v>
+        <v>0.21497</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>31.488603</v>
+        <v>0.495797</v>
       </c>
     </row>
     <row r="49">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -23334,7 +23334,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -23409,7 +23409,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -27887,7 +27887,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E318" s="5" t="n">

--- a/output/pdf_financials_xlsx/MMA.xlsx
+++ b/output/pdf_financials_xlsx/MMA.xlsx
@@ -15634,7 +15634,11 @@
           <t>Proceeds from Private Placement</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
